--- a/LanguaGeSystem/model/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/LanguaGeSystem/model/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="20"/>
@@ -2502,6 +2502,300 @@
         <v>10518</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10519</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>10519</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10520</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>10520</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10521</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>10521</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10522</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>10522</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10523</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>10523</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10524</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>10524</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18" type="list">
@@ -2521,7 +2815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="20"/>
@@ -3765,6 +4059,300 @@
         <v>10518</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10519</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>10519</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10520</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>10520</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10521</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>10521</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10522</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>10522</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10523</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>10523</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10524</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>10524</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
